--- a/4981_Intercuenca_Bajo_Maranon/_raw_reportes_xlsx/IDConfig_65378_completo.xlsx
+++ b/4981_Intercuenca_Bajo_Maranon/_raw_reportes_xlsx/IDConfig_65378_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R98df14aa65114830"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3f6609c33dee48f2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9425</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0075</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1575</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.3325</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4725</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/4981_Intercuenca_Bajo_Maranon/_raw_reportes_xlsx/IDConfig_65378_completo.xlsx
+++ b/4981_Intercuenca_Bajo_Maranon/_raw_reportes_xlsx/IDConfig_65378_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3f6609c33dee48f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R15897332f10444eb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.3075</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.1825</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.1225</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.1825</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.2825</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.3875</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5025</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6575</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.8075</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.0975</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3525</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4075</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.7525</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5125</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5025</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4425</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4975</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.8075</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.9125</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.0275</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1725</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4475</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5725</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1975</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0475</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8725</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
